--- a/5/search/FY4_Missile1_results/all_solutions.xlsx
+++ b/5/search/FY4_Missile1_results/all_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,37 +487,352 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>315</v>
+        <v>216</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9381.966011250104</v>
+      </c>
+      <c r="F2" t="n">
+        <v>824.4294954150539</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8249.342219125178</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.530142205591687</v>
+      </c>
+      <c r="J2" t="n">
+        <v>839.5999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>216</v>
+      </c>
+      <c r="B3" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9550.241546080095</v>
+      </c>
+      <c r="F3" t="n">
+        <v>946.6888278918884</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8281.702898900177</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.04155229729076</v>
+      </c>
+      <c r="J3" t="n">
+        <v>839.5999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>124</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10355.74753605646</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1245.677282124769</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9308.837282148203</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19.90286557751892</v>
+      </c>
+      <c r="J4" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>128</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12092.90424100193</v>
-      </c>
-      <c r="F2" t="n">
-        <v>907.0957589980717</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13003.6577751702</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-3.65777517020183</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1310</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="E5" t="n">
+        <v>10880.47597370578</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1502.146600756389</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10521.9038948231</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.586403025558184</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>261</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10874.85242796781</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1209.84932752389</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10687.13106991954</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.62331880972465</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>261</v>
+      </c>
+      <c r="B7" t="n">
+        <v>124</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10922.40850534004</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1510.106583064812</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10689.63402136018</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40.42633225924692</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>122</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10961.71196128481</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1513.504341138233</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10846.84784513925</v>
+      </c>
+      <c r="I8" t="n">
+        <v>54.01736455293417</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>288</v>
+      </c>
+      <c r="B9" t="n">
+        <v>140</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11173.04951684997</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1467.408350874714</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11648.93568818739</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.781315780177465</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>114</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11349.00729031696</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1157.421866349707</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11828.89231450279</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.12306741944667</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>297</v>
+      </c>
+      <c r="B11" t="n">
+        <v>116</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11421.3031837583</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1173.145945553194</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12000.59506142596</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36.22162068883677</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
